--- a/originales/respuestas/2025/01. Calificadas/bucle p28/Alcaldía Local De Tunjuelito.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/bucle p28/Alcaldía Local De Tunjuelito.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/Desktop/Esteban 2/bucle p28/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0E806534-26CA-48F1-A3A0-1A70989FC21B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D92AD427-1BEA-B54E-B390-ED74A31E8A16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{39E954F8-589B-484C-BF77-02CA1F8201F3}"/>
+    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" xr2:uid="{39E954F8-589B-484C-BF77-02CA1F8201F3}"/>
   </bookViews>
   <sheets>
     <sheet name="Entidad" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>Entidad</t>
   </si>
@@ -155,45 +155,6 @@
   </si>
   <si>
     <t>Soporte documental y trazabilidad</t>
-  </si>
-  <si>
-    <t>· Optimizar el trámite de cuenta de cobro: TunjoWallet busca simplificar y agilizar el 
- proceso de generación de formatos, revisión, aprobación y seguimiento de cuentas 
- de cobro, minimizando el tiempo y los recursos requeridos para este fin.
- · Automatización de carga de información: Facilita la automatización de carga de 
- datos de contratistas y contratos para generar los formatos requeridos por la entidad 
- correspondiente.
- · Reducción del consumo de papel y tiempo: Contribuye a la reducción de consumo 
- de papel al generar de forma digital los documentos y/o formatos del trámite de 
- cuenta de cobro; así mismo optimiza el tiempo de creación y flujo de revisión hasta 
- la aprobación.
- · Control y supervisión efectiva: Permite tener control más efectivo y una supervisión 
- transparente del estado de trámite de cuenta de cobro persona natural.
- · Facilitar la interacción entre usuarios: Proporciona una plataforma colaborativa 
- donde los diferentes actores involucrados en el proceso de trámite de cuenta de 
- cobro, pueden interactuar de manera efectiva, comparanendo información y 
- realizando seguimiento en Ɵempo real.</t>
-  </si>
-  <si>
-    <t>La Alcaldia Local de Tunjuelito funciona como Fondo de Desarrollo Local, el cual depende de la Secretaría Distrital de Gobierno de la Alcaldía Mayor de Bogotá, nuestra estructura organizacional, no tiene una unidad especifica de innovación.</t>
-  </si>
-  <si>
-    <t>· Optimizar el trámite de cuenta de cobro: TunjoWallet busca simplificar y agilizar el 
- proceso de generación de formatos, revisión, aprobación y seguimiento de cuentas 
- de cobro, minimizando el tiempo y los recursos requeridos para este fin.
- · Automatización de carga de información: Facilita la automatización de carga de 
- datos de contratistas y contratos para generar los formatos requeridos por la entidad 
- correspondiente.
- · Reducción del consumo de papel y tiempo: Contribuye a la reducción de consumo 
- de papel al generar de forma digital los documentos y/o formatos del trámite de 
- cuenta de cobro; así mismo optimiza el tiempo de creación y flujo de revisión hasta 
- la aprobación.
- · Control y supervisión efectiva: Permite tener control más efectivo y una supervisión 
- transparente del estado de trámite de cuenta de cobro persona natural.
- · Facilitar la interacción entre usuarios: Proporciona una plataforma colaborativa 
- donde los diferentes actores involucrados en el proceso de trámite de cuenta de 
- cobro, pueden interactuar de manera efectiva, comparando información y 
- realizando seguimiento en tiempo real.</t>
   </si>
 </sst>
 </file>
@@ -212,11 +173,13 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -322,9 +285,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -641,10 +606,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECB73A83-9530-4280-A199-F0135BA824A6}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:V4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:V2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:22" ht="50" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" ht="56" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -712,169 +677,71 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:22" ht="50" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:22" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="M2" s="5">
-        <v>5</v>
-      </c>
-      <c r="N2" s="5" t="s">
+      <c r="M2" s="4">
+        <v>3</v>
+      </c>
+      <c r="N2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="O2" s="5">
-        <v>5</v>
-      </c>
-      <c r="P2" s="5" t="s">
+      <c r="O2" s="4">
+        <v>3</v>
+      </c>
+      <c r="P2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="Q2" s="5">
-        <v>5</v>
-      </c>
-      <c r="R2" s="5" t="s">
+      <c r="Q2" s="4">
+        <v>3</v>
+      </c>
+      <c r="R2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="S2" s="5">
-        <v>5</v>
-      </c>
-      <c r="T2" s="5" t="s">
+      <c r="S2" s="4">
+        <v>3</v>
+      </c>
+      <c r="T2" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="U2" s="5">
-        <v>5</v>
-      </c>
-      <c r="V2" s="5"/>
-    </row>
-    <row r="3" spans="1:22" ht="50" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="M3" s="5">
-        <v>5</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="O3" s="5">
-        <v>5</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q3" s="5">
-        <v>5</v>
-      </c>
-      <c r="R3" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="S3" s="5">
-        <v>5</v>
-      </c>
-      <c r="T3" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="U3" s="5">
-        <v>5</v>
-      </c>
-      <c r="V3" s="5"/>
-    </row>
-    <row r="4" spans="1:22" ht="50" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="M4" s="5">
-        <v>5</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="O4" s="5">
-        <v>5</v>
-      </c>
-      <c r="P4" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q4" s="5">
-        <v>5</v>
-      </c>
-      <c r="R4" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="S4" s="5">
-        <v>5</v>
-      </c>
-      <c r="T4" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="U4" s="5">
-        <v>5</v>
-      </c>
-      <c r="V4" s="5"/>
+      <c r="U2" s="4">
+        <v>3</v>
+      </c>
+      <c r="V2" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/originales/respuestas/2025/01. Calificadas/bucle p28/Alcaldía Local De Tunjuelito.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/bucle p28/Alcaldía Local De Tunjuelito.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/Desktop/Esteban 2/bucle p28/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/Downloads/IIP - Esteban/bucle p28/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D92AD427-1BEA-B54E-B390-ED74A31E8A16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{221BF57E-EED2-114B-AD66-1DFD55F00E89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" xr2:uid="{39E954F8-589B-484C-BF77-02CA1F8201F3}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16680" xr2:uid="{39E954F8-589B-484C-BF77-02CA1F8201F3}"/>
   </bookViews>
   <sheets>
     <sheet name="Entidad" sheetId="1" r:id="rId1"/>
@@ -161,7 +161,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -180,6 +180,14 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -271,10 +279,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -291,8 +300,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -708,7 +721,7 @@
       <c r="J2" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="6" t="s">
         <v>32</v>
       </c>
       <c r="L2" s="4" t="s">
@@ -744,6 +757,9 @@
       <c r="V2" s="4"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="K2" r:id="rId1" xr:uid="{E02B1CB0-41D0-544F-B485-2805307E616B}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>